--- a/peer_evaluation_forms/003_faculty_peer_resource_exchange_registration_form--peer_evaluation_forms.xlsx
+++ b/peer_evaluation_forms/003_faculty_peer_resource_exchange_registration_form--peer_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'arts_and_sciences',_'label':_'arts_and_sciences'}</t>
+          <t>arts_and_sciences</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Arts and Sciences', 'label': 'Arts and Sciences'}</t>
+          <t>Arts and Sciences</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'business',_'label':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Business', 'label': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'engineering',_'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Engineering', 'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'moses',_'label':_'moses'}</t>
+          <t>moses</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Moses', 'label': 'Moses'}</t>
+          <t>Moses</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'elijah',_'label':_'elijah'}</t>
+          <t>elijah</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Elijah', 'label': 'Elijah'}</t>
+          <t>Elijah</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'abraham',_'label':_'abraham'}</t>
+          <t>abraham</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Abraham', 'label': 'Abraham'}</t>
+          <t>Abraham</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'computer_science',_'label':_'computer_science'}</t>
+          <t>computer_science</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Computer Science', 'label': 'Computer Science'}</t>
+          <t>Computer Science</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'physics',_'label':_'physics'}</t>
+          <t>physics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Physics', 'label': 'Physics'}</t>
+          <t>Physics</t>
         </is>
       </c>
     </row>
@@ -1106,165 +1106,165 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'mathematics',_'label':_'mathematics'}</t>
+          <t>mathematics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Mathematics', 'label': 'Mathematics'}</t>
+          <t>Mathematics</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'arts',_'label':_'arts'}</t>
+          <t>arts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Arts', 'label': 'Arts'}</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'engineering',_'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Engineering', 'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'business',_'label':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Business', 'label': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'business',_'label':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Business', 'label': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'engineering',_'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Engineering', 'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'arts',_'label':_'arts'}</t>
+          <t>arts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Arts', 'label': 'Arts'}</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'arts',_'label':_'arts'}</t>
+          <t>arts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Arts', 'label': 'Arts'}</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'engineering',_'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Engineering', 'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'business',_'label':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Business', 'label': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
